--- a/Data/RemapDrafts/JeanRemapDraft.xlsx
+++ b/Data/RemapDrafts/JeanRemapDraft.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264846FC-4AC1-44C0-B04A-744BEA7E3CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6B7D9E-F21F-46C9-BB6A-8E4B651558E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="3" xr2:uid="{B08DB923-5719-4BE6-B084-9B7B07E846C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{B08DB923-5719-4BE6-B084-9B7B07E846C8}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 Jean to JeanSeaBreeze" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.0 JeanCN to JeanSeaBreeze" sheetId="2" r:id="rId2"/>
-    <sheet name="V4.0 JeanSeaBreeze to JeanCN" sheetId="3" r:id="rId3"/>
-    <sheet name="V4.0 JeanSeaBreeze to Jean" sheetId="5" r:id="rId4"/>
+    <sheet name="Credits" sheetId="6" r:id="rId1"/>
+    <sheet name="V4.0 Jean to JeanSeaBreeze" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.0 JeanCN to JeanSeaBreeze" sheetId="2" r:id="rId3"/>
+    <sheet name="V4.0 JeanSeaBreeze to JeanCN" sheetId="3" r:id="rId4"/>
+    <sheet name="V4.0 JeanSeaBreeze to Jean" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 Jean to JeanSeaBreeze'!$A$1:$D$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 JeanCN to JeanSeaBreeze'!$A$1:$D$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'V4.0 JeanSeaBreeze to Jean'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 JeanSeaBreeze to JeanCN'!$A$1:$D$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 Jean to JeanSeaBreeze'!$A$1:$D$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 JeanCN to JeanSeaBreeze'!$A$1:$D$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'V4.0 JeanSeaBreeze to Jean'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'V4.0 JeanSeaBreeze to JeanCN'!$A$1:$D$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="57">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -207,13 +208,22 @@
   </si>
   <si>
     <t>JeanSea's left upper leg</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +234,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -247,14 +273,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -607,6 +637,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C505B40-5618-4434-B48A-F4A4BB488B0D}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{F7C70B62-89AB-4EB2-A253-BE9B477BE7BD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49AB671E-7818-43C8-8102-667B1AED1333}">
   <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1610,7 +1671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EFCF4D-ADFC-4791-85F3-0ABE39B0B46F}">
   <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2534,7 +2595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406AA0E2-DCFE-41DE-8EFA-24808C8E601D}">
   <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3297,7 +3358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8AA5F56-F749-41C7-A993-BD2A5016016C}">
   <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
